--- a/config/EGX_Stock_Groups.xlsx
+++ b/config/EGX_Stock_Groups.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$78</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$79</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="101">
   <si>
     <t>Sector</t>
   </si>
@@ -322,6 +322,9 @@
   </si>
   <si>
     <t>BIGP</t>
+  </si>
+  <si>
+    <t>SIPC</t>
   </si>
 </sst>
 </file>
@@ -654,7 +657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C78"/>
+  <dimension ref="A1:C79"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -1355,13 +1358,13 @@
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
@@ -1369,18 +1372,18 @@
         <v>54</v>
       </c>
       <c r="B65" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C65" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>54</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>82</v>
+      <c r="B66" t="s">
+        <v>81</v>
       </c>
       <c r="C66" t="s">
         <v>90</v>
@@ -1390,8 +1393,8 @@
       <c r="A67" t="s">
         <v>54</v>
       </c>
-      <c r="B67" s="1" t="s">
-        <v>83</v>
+      <c r="B67" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C67" t="s">
         <v>90</v>
@@ -1399,10 +1402,10 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>40</v>
-      </c>
-      <c r="B68" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C68" t="s">
         <v>90</v>
@@ -1412,52 +1415,52 @@
       <c r="A69" t="s">
         <v>40</v>
       </c>
-      <c r="B69" s="1" t="s">
-        <v>41</v>
+      <c r="B69" t="s">
+        <v>42</v>
       </c>
       <c r="C69" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C70" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>55</v>
       </c>
-      <c r="B71" t="s">
-        <v>99</v>
+      <c r="B71" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B72" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C72" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>57</v>
       </c>
-      <c r="B73" s="1" t="s">
-        <v>86</v>
+      <c r="B73" t="s">
+        <v>98</v>
       </c>
       <c r="C73" t="s">
         <v>90</v>
@@ -1467,8 +1470,8 @@
       <c r="A74" t="s">
         <v>57</v>
       </c>
-      <c r="B74" t="s">
-        <v>87</v>
+      <c r="B74" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C74" t="s">
         <v>90</v>
@@ -1479,7 +1482,7 @@
         <v>57</v>
       </c>
       <c r="B75" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C75" t="s">
         <v>90</v>
@@ -1487,13 +1490,13 @@
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C76" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
@@ -1501,20 +1504,31 @@
         <v>56</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C77" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>56</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B79" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C78" t="s">
+      <c r="C79" t="s">
         <v>90</v>
       </c>
     </row>

--- a/config/EGX_Stock_Groups.xlsx
+++ b/config/EGX_Stock_Groups.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$C$80</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="237" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="103">
   <si>
     <t>Sector</t>
   </si>
@@ -325,6 +325,12 @@
   </si>
   <si>
     <t>SIPC</t>
+  </si>
+  <si>
+    <t>ISMQ</t>
+  </si>
+  <si>
+    <t>BONY</t>
   </si>
 </sst>
 </file>
@@ -657,7 +663,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C79"/>
+  <dimension ref="A1:C81"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
@@ -1237,13 +1243,13 @@
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="C53" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:3" x14ac:dyDescent="0.25">
@@ -1251,10 +1257,10 @@
         <v>53</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.25">
@@ -1262,29 +1268,29 @@
         <v>53</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>78</v>
+        <v>38</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="C56" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>2</v>
       </c>
-      <c r="B57" t="s">
-        <v>79</v>
+      <c r="B57" s="1" t="s">
+        <v>3</v>
       </c>
       <c r="C57" t="s">
         <v>89</v>
@@ -1294,8 +1300,8 @@
       <c r="A58" t="s">
         <v>2</v>
       </c>
-      <c r="B58" s="1" t="s">
-        <v>46</v>
+      <c r="B58" t="s">
+        <v>79</v>
       </c>
       <c r="C58" t="s">
         <v>89</v>
@@ -1306,10 +1312,10 @@
         <v>2</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="C59" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.25">
@@ -1317,18 +1323,18 @@
         <v>2</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C60" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>2</v>
       </c>
-      <c r="B61" t="s">
-        <v>4</v>
+      <c r="B61" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C61" t="s">
         <v>90</v>
@@ -1339,7 +1345,7 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C62" t="s">
         <v>90</v>
@@ -1349,33 +1355,33 @@
       <c r="A63" t="s">
         <v>2</v>
       </c>
-      <c r="B63" s="1" t="s">
-        <v>7</v>
+      <c r="B63" t="s">
+        <v>5</v>
       </c>
       <c r="C63" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>2</v>
       </c>
-      <c r="B64" t="s">
-        <v>100</v>
+      <c r="B64" s="1" t="s">
+        <v>7</v>
       </c>
       <c r="C64" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="C65" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.25">
@@ -1383,18 +1389,18 @@
         <v>54</v>
       </c>
       <c r="B66" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C66" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>54</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>82</v>
+      <c r="B67" t="s">
+        <v>81</v>
       </c>
       <c r="C67" t="s">
         <v>90</v>
@@ -1404,8 +1410,8 @@
       <c r="A68" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="1" t="s">
-        <v>83</v>
+      <c r="B68" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="C68" t="s">
         <v>90</v>
@@ -1413,10 +1419,10 @@
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>40</v>
-      </c>
-      <c r="B69" t="s">
-        <v>42</v>
+        <v>54</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="C69" t="s">
         <v>90</v>
@@ -1426,52 +1432,52 @@
       <c r="A70" t="s">
         <v>40</v>
       </c>
-      <c r="B70" s="1" t="s">
-        <v>41</v>
+      <c r="B70" t="s">
+        <v>42</v>
       </c>
       <c r="C70" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>84</v>
+        <v>41</v>
       </c>
       <c r="C71" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>55</v>
       </c>
-      <c r="B72" t="s">
-        <v>99</v>
+      <c r="B72" s="1" t="s">
+        <v>84</v>
       </c>
       <c r="C72" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B73" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C73" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>57</v>
       </c>
-      <c r="B74" s="1" t="s">
-        <v>86</v>
+      <c r="B74" t="s">
+        <v>98</v>
       </c>
       <c r="C74" t="s">
         <v>90</v>
@@ -1481,8 +1487,8 @@
       <c r="A75" t="s">
         <v>57</v>
       </c>
-      <c r="B75" t="s">
-        <v>87</v>
+      <c r="B75" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="C75" t="s">
         <v>90</v>
@@ -1493,7 +1499,7 @@
         <v>57</v>
       </c>
       <c r="B76" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="C76" t="s">
         <v>90</v>
@@ -1501,13 +1507,13 @@
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B77" t="s">
-        <v>92</v>
+        <v>97</v>
       </c>
       <c r="C77" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.25">
@@ -1515,20 +1521,42 @@
         <v>56</v>
       </c>
       <c r="B78" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C78" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>56</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" t="s">
+        <v>93</v>
+      </c>
+      <c r="C79" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>56</v>
+      </c>
+      <c r="B80" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>9</v>
+      </c>
+      <c r="B81" t="s">
+        <v>102</v>
+      </c>
+      <c r="C81" t="s">
         <v>90</v>
       </c>
     </row>
